--- a/inh-seo/docs/collection-worksheet.xlsx
+++ b/inh-seo/docs/collection-worksheet.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Mechanical Fixes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Collections'!$A$1:$T$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Collections'!$A$1:$T$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  67 collections are in this worksheet.</t>
+          <t xml:space="preserve">  66 collections are in this worksheet.</t>
         </is>
       </c>
     </row>
@@ -546,21 +546,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs a NEW SEO TITLE:        54 of 67   (13 already have one — leave those blank)</t>
+          <t xml:space="preserve">  Needs a NEW SEO TITLE:        53 of 66   (13 already have one — leave those blank)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs a NEW META DESCRIPTION: 16 of 67   (51 already have one)</t>
+          <t xml:space="preserve">  Needs a NEW META DESCRIPTION: 15 of 66   (51 already have one)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs a DESCRIPTION:          64 of 67   (3 already written)</t>
+          <t xml:space="preserve">  Needs a DESCRIPTION:          63 of 66   (3 already written)</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  23 rows were dropped from the 90-collection plan:</t>
+          <t xml:space="preserve">  24 rows were dropped from the 90-collection plan:</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    10 unpublished from the Online Store (Round 1.5 and earlier)</t>
+          <t xml:space="preserve">    11 unpublished from the Online Store (Round 1.5 and earlier)</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  20 of 67 collections got ZERO. Total across all rows: 2,778 impressions, 5 clicks.</t>
+          <t xml:space="preserve">  19 of 66 collections got ZERO. Total across all rows: 2,778 impressions, 5 clicks.</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T68"/>
+  <dimension ref="A1:T67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2346,7 +2346,7 @@
       <c r="S21" s="9" t="inlineStr"/>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>EMF HUB. See cannibalisation note. | Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
+          <t>EMF HUB. See cannibalisation note. | Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json. | EMF ruling 7 September 2026: the three EMF collections STAY as three. Client's call - genuinely different products for different buyers, not one thing split three ways. The Round 2 hub-and-spoke plan (low-emf as canonical hub, the other two as children) is DROPPED; it was built on the assumption they were duplicates. Each description must OPEN by stating what its tier means in mG, so the pages are distinguishable to a reader and to Google. Cross-link all three as siblings, each to the other two.</t>
         </is>
       </c>
     </row>
@@ -2356,17 +2356,17 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>newest-products</t>
+          <t>best-selling-products</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/newest-products</t>
+          <t>https://inhousewellness.com/collections/best-selling-products</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Newest Products</t>
+          <t>Best Selling Products</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>KEEP_TOP_20</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       <c r="S22" s="9" t="inlineStr"/>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>Client decision: this becomes the general 'Products' collection, OR is unpublished in favour of the native /collections/all which Shopify provides free. Confirm which before running.</t>
+          <t>KEEP. Limit to top 20 products. Shopify collections have no product cap — this needs either a manual collection kept in sync from order data (requires read_orders scope) or a theme-level render limit. See TASKS.md.</t>
         </is>
       </c>
     </row>
@@ -2420,21 +2420,21 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>best-selling-products</t>
+          <t>chromotherapy</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/best-selling-products</t>
+          <t>https://inhousewellness.com/collections/chromotherapy</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Best Selling Products</t>
+          <t>Chromotherapy</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>673</v>
+        <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -2456,16 +2456,20 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>KEEP_TOP_20</t>
+          <t>WRITE</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>chromotherapy sauna</t>
+        </is>
+      </c>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="8" t="inlineStr"/>
       <c r="P23" s="8" t="inlineStr"/>
@@ -2474,7 +2478,7 @@
       <c r="S23" s="9" t="inlineStr"/>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>KEEP. Limit to top 20 products. Shopify collections have no product cap — this needs either a manual collection kept in sync from order data (requires read_orders scope) or a theme-level render limit. See TASKS.md.</t>
+          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
         </is>
       </c>
     </row>
@@ -2484,24 +2488,24 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>chromotherapy</t>
+          <t>golden-designs</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/chromotherapy</t>
+          <t>https://inhousewellness.com/collections/golden-designs</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Chromotherapy</t>
+          <t>Golden Designs</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -2510,7 +2514,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -2520,7 +2524,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -2531,7 +2535,7 @@
       <c r="L24" s="8" t="inlineStr"/>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>chromotherapy sauna</t>
+          <t>golden designs sauna</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr"/>
@@ -2542,7 +2546,7 @@
       <c r="S24" s="9" t="inlineStr"/>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
+          <t>SEO title has a duplication bug: '...WellnessGolden Designs'.</t>
         </is>
       </c>
     </row>
@@ -2552,24 +2556,24 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>golden-designs</t>
+          <t>sauna-accessories</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/golden-designs</t>
+          <t>https://inhousewellness.com/collections/sauna-accessories</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Golden Designs</t>
+          <t>Sauna Accessories</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -2578,7 +2582,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2588,7 +2592,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -2599,7 +2603,7 @@
       <c r="L25" s="8" t="inlineStr"/>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>golden designs sauna</t>
+          <t>sauna accessories</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr"/>
@@ -2608,11 +2612,7 @@
       <c r="Q25" s="9" t="inlineStr"/>
       <c r="R25" s="9" t="inlineStr"/>
       <c r="S25" s="9" t="inlineStr"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>SEO title has a duplication bug: '...WellnessGolden Designs'.</t>
-        </is>
-      </c>
+      <c r="T25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>sauna-accessories</t>
+          <t>huum-sauna-heaters</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/sauna-accessories</t>
+          <t>https://inhousewellness.com/collections/huum-sauna-heaters</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Sauna Accessories</t>
+          <t>Huum Sauna Heaters</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>4</v>
+        <v>264</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
@@ -2651,14 +2651,10 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -2667,7 +2663,7 @@
       <c r="L26" s="8" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>sauna accessories</t>
+          <t>huum sauna heater</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr"/>
@@ -2676,7 +2672,11 @@
       <c r="Q26" s="9" t="inlineStr"/>
       <c r="R26" s="9" t="inlineStr"/>
       <c r="S26" s="9" t="inlineStr"/>
-      <c r="T26" s="7" t="inlineStr"/>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>No SEO title or meta.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -2684,24 +2684,24 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>huum-sauna-heaters</t>
+          <t>maxxus</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/huum-sauna-heaters</t>
+          <t>https://inhousewellness.com/collections/maxxus</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Huum Sauna Heaters</t>
+          <t>Maxxus Saunas</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>264</v>
+        <v>118</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -2715,10 +2715,14 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -2727,7 +2731,7 @@
       <c r="L27" s="8" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>huum sauna heater</t>
+          <t>maxxus sauna</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr"/>
@@ -2738,7 +2742,7 @@
       <c r="S27" s="9" t="inlineStr"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>No SEO title or meta.</t>
+          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
         </is>
       </c>
     </row>
@@ -2748,24 +2752,24 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>maxxus</t>
+          <t>steam-showers</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/maxxus</t>
+          <t>https://inhousewellness.com/collections/steam-showers</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Maxxus Saunas</t>
+          <t>Steam Showers</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
@@ -2795,7 +2799,7 @@
       <c r="L28" s="8" t="inlineStr"/>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>maxxus sauna</t>
+          <t>steam shower</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr"/>
@@ -2806,7 +2810,7 @@
       <c r="S28" s="9" t="inlineStr"/>
       <c r="T28" s="7" t="inlineStr">
         <is>
-          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
+          <t>Has copy but with data-start/data-end markup residue. No SEO fields. | Description cleared 2026-09-07: contained health claims that would have become visible when the theme render fix ships. Needs new copy. | Meta written 2026-09-07: description was cleared (health claims) leaving no meta source; 27 products should not sit on the generic fallback.</t>
         </is>
       </c>
     </row>
@@ -2816,24 +2820,24 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>steam-showers</t>
+          <t>near-zero-emf</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/steam-showers</t>
+          <t>https://inhousewellness.com/collections/near-zero-emf</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Steam Showers</t>
+          <t>Near Zero EMF Saunas</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -2847,10 +2851,14 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -2859,7 +2867,7 @@
       <c r="L29" s="8" t="inlineStr"/>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>steam shower</t>
+          <t>near zero emf sauna</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr"/>
@@ -2870,7 +2878,7 @@
       <c r="S29" s="9" t="inlineStr"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>Has copy but with data-start/data-end markup residue. No SEO fields. | Description cleared 2026-09-07: contained health claims that would have become visible when the theme render fix ships. Needs new copy. | Meta written 2026-09-07: description was cleared (health claims) leaving no meta source; 27 products should not sit on the generic fallback.</t>
+          <t>EMF child. Canonical up to /low-emf. | Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json. | EMF ruling 7 September 2026: the three EMF collections STAY as three. Client's call - genuinely different products for different buyers, not one thing split three ways. The Round 2 hub-and-spoke plan (low-emf as canonical hub, the other two as children) is DROPPED; it was built on the assumption they were duplicates. Each description must OPEN by stating what its tier means in mG, so the pages are distinguishable to a reader and to Google. Cross-link all three as siblings, each to the other two.</t>
         </is>
       </c>
     </row>
@@ -2880,24 +2888,24 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>near-zero-emf</t>
+          <t>medical-sauna</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/near-zero-emf</t>
+          <t>https://inhousewellness.com/collections/medical-sauna</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Near Zero EMF Saunas</t>
+          <t>Medical Sauna</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
         <v>24</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
@@ -2906,7 +2914,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2916,7 +2924,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2927,7 +2935,7 @@
       <c r="L30" s="8" t="inlineStr"/>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>near zero emf sauna</t>
+          <t>medical sauna</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr"/>
@@ -2938,7 +2946,7 @@
       <c r="S30" s="9" t="inlineStr"/>
       <c r="T30" s="7" t="inlineStr">
         <is>
-          <t>EMF child. Canonical up to /low-emf. | Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
+          <t>SEO copy describes cold plunges, not saunas. Mismatch.</t>
         </is>
       </c>
     </row>
@@ -2948,24 +2956,24 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>medical-sauna</t>
+          <t>ultra-low-emf</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/medical-sauna</t>
+          <t>https://inhousewellness.com/collections/ultra-low-emf</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Medical Sauna</t>
+          <t>Ultra Low EMF Saunas</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
@@ -2974,7 +2982,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -2984,7 +2992,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2995,18 +3003,20 @@
       <c r="L31" s="8" t="inlineStr"/>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>medical sauna</t>
+          <t>ultra low emf sauna</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr"/>
-      <c r="O31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="n">
+        <v>30.02</v>
+      </c>
       <c r="P31" s="8" t="inlineStr"/>
       <c r="Q31" s="9" t="inlineStr"/>
       <c r="R31" s="9" t="inlineStr"/>
       <c r="S31" s="9" t="inlineStr"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>SEO copy describes cold plunges, not saunas. Mismatch.</t>
+          <t>HIGHEST CPC IN CATALOG. EMF child. | EMF ruling 7 September 2026: the three EMF collections STAY as three. Client's call - genuinely different products for different buyers, not one thing split three ways. The Round 2 hub-and-spoke plan (low-emf as canonical hub, the other two as children) is DROPPED; it was built on the assumption they were duplicates. Each description must OPEN by stating what its tier means in mG, so the pages are distinguishable to a reader and to Google. Cross-link all three as siblings, each to the other two.</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3026,24 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ultra-low-emf</t>
+          <t>sauna-life</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/ultra-low-emf</t>
+          <t>https://inhousewellness.com/collections/sauna-life</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Ultra Low EMF Saunas</t>
+          <t>Sauna Life</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
         <v>22</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
@@ -3047,14 +3057,10 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr"/>
       <c r="K32" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -3063,20 +3069,18 @@
       <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>ultra low emf sauna</t>
+          <t>sauna life</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr"/>
-      <c r="O32" s="8" t="n">
-        <v>30.02</v>
-      </c>
+      <c r="O32" s="8" t="inlineStr"/>
       <c r="P32" s="8" t="inlineStr"/>
       <c r="Q32" s="9" t="inlineStr"/>
       <c r="R32" s="9" t="inlineStr"/>
       <c r="S32" s="9" t="inlineStr"/>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>HIGHEST CPC IN CATALOG. EMF child.</t>
+          <t>No SEO title or meta.</t>
         </is>
       </c>
     </row>
@@ -3086,25 +3090,25 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>sauna-life</t>
+          <t>dynamic-cold-therapy</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/sauna-life</t>
+          <t>https://inhousewellness.com/collections/dynamic-cold-therapy</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Sauna Life</t>
+          <t>Dynamic Cold Therapy</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F33" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F33" s="6" t="n">
-        <v>49</v>
-      </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
           <t>empty</t>
@@ -3117,10 +3121,14 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -3129,7 +3137,7 @@
       <c r="L33" s="8" t="inlineStr"/>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>sauna life</t>
+          <t>dynamic cold therapy</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr"/>
@@ -3140,7 +3148,7 @@
       <c r="S33" s="9" t="inlineStr"/>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>No SEO title or meta.</t>
+          <t>Heavy Tailwind/ChatGPT markup residue in live copy. | Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json. | Description cleared 2026-09-07: contained health claims that would have become visible when the theme render fix ships. Needs new copy.</t>
         </is>
       </c>
     </row>
@@ -3150,24 +3158,24 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>dynamic-cold-therapy</t>
+          <t>massage-chairs</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/dynamic-cold-therapy</t>
+          <t>https://inhousewellness.com/collections/massage-chairs</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Dynamic Cold Therapy</t>
+          <t>Massage Chairs</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
@@ -3197,7 +3205,7 @@
       <c r="L34" s="8" t="inlineStr"/>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>dynamic cold therapy</t>
+          <t>massage chair</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr"/>
@@ -3208,7 +3216,7 @@
       <c r="S34" s="9" t="inlineStr"/>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>Heavy Tailwind/ChatGPT markup residue in live copy. | Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json. | Description cleared 2026-09-07: contained health claims that would have become visible when the theme render fix ships. Needs new copy.</t>
+          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
         </is>
       </c>
     </row>
@@ -3218,24 +3226,24 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>massage-chairs</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/massage-chairs</t>
+          <t>https://inhousewellness.com/collections/hybrid</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Massage Chairs</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
@@ -3249,14 +3257,10 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr"/>
       <c r="K35" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -3265,7 +3269,7 @@
       <c r="L35" s="8" t="inlineStr"/>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>massage chair</t>
+          <t>hybrid sauna</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr"/>
@@ -3276,7 +3280,7 @@
       <c r="S35" s="9" t="inlineStr"/>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
+          <t>No SEO title or meta.</t>
         </is>
       </c>
     </row>
@@ -3286,24 +3290,24 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>frontpage</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/hybrid</t>
+          <t>https://inhousewellness.com/collections/frontpage</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Home page</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
@@ -3317,21 +3321,21 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>WRITE</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>hybrid sauna</t>
-        </is>
-      </c>
+      <c r="M36" s="9" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
       <c r="O36" s="8" t="inlineStr"/>
       <c r="P36" s="8" t="inlineStr"/>
@@ -3340,7 +3344,7 @@
       <c r="S36" s="9" t="inlineStr"/>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>No SEO title or meta.</t>
+          <t>Theme homepage collection. Not an SEO target.</t>
         </is>
       </c>
     </row>
@@ -3350,24 +3354,24 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>frontpage</t>
+          <t>dreampod</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/frontpage</t>
+          <t>https://inhousewellness.com/collections/dreampod</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Home page</t>
+          <t>Dreampod</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
@@ -3376,7 +3380,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -3386,27 +3390,27 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WRITE</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr"/>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>dreampod</t>
+        </is>
+      </c>
       <c r="N37" s="8" t="inlineStr"/>
       <c r="O37" s="8" t="inlineStr"/>
       <c r="P37" s="8" t="inlineStr"/>
       <c r="Q37" s="9" t="inlineStr"/>
       <c r="R37" s="9" t="inlineStr"/>
       <c r="S37" s="9" t="inlineStr"/>
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>Theme homepage collection. Not an SEO target.</t>
-        </is>
-      </c>
+      <c r="T37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -3414,24 +3418,24 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>dreampod</t>
+          <t>cold-plunge-cooling-system</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/dreampod</t>
+          <t>https://inhousewellness.com/collections/cold-plunge-cooling-system</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Dreampod</t>
+          <t>Cold Plunge Cooling System</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
@@ -3461,7 +3465,7 @@
       <c r="L38" s="8" t="inlineStr"/>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>dreampod</t>
+          <t>cold plunge chiller</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr"/>
@@ -3478,24 +3482,24 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>cold-plunge-cooling-system</t>
+          <t>narvi</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/cold-plunge-cooling-system</t>
+          <t>https://inhousewellness.com/collections/narvi</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Cold Plunge Cooling System</t>
+          <t>Narvi</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
@@ -3504,19 +3508,15 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>title + meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -3525,7 +3525,7 @@
       <c r="L39" s="8" t="inlineStr"/>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>cold plunge chiller</t>
+          <t>narvi sauna heater</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr"/>
@@ -3534,7 +3534,11 @@
       <c r="Q39" s="9" t="inlineStr"/>
       <c r="R39" s="9" t="inlineStr"/>
       <c r="S39" s="9" t="inlineStr"/>
-      <c r="T39" s="7" t="inlineStr"/>
+      <c r="T39" s="7" t="inlineStr">
+        <is>
+          <t>No SEO title or meta.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -3542,24 +3546,24 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>narvi</t>
+          <t>leisurecraft</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/narvi</t>
+          <t>https://inhousewellness.com/collections/leisurecraft</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Narvi</t>
+          <t>Dundalk LeisureCraft</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
@@ -3573,10 +3577,14 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -3585,7 +3593,7 @@
       <c r="L40" s="8" t="inlineStr"/>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>narvi sauna heater</t>
+          <t>dundalk leisurecraft sauna</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr"/>
@@ -3594,11 +3602,7 @@
       <c r="Q40" s="9" t="inlineStr"/>
       <c r="R40" s="9" t="inlineStr"/>
       <c r="S40" s="9" t="inlineStr"/>
-      <c r="T40" s="7" t="inlineStr">
-        <is>
-          <t>No SEO title or meta.</t>
-        </is>
-      </c>
+      <c r="T40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -3606,24 +3610,24 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>leisurecraft</t>
+          <t>scandia-manufacturing</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/leisurecraft</t>
+          <t>https://inhousewellness.com/collections/scandia-manufacturing</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Dundalk LeisureCraft</t>
+          <t>Scandia Sauna Heaters</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>123</v>
+        <v>189</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
@@ -3653,7 +3657,7 @@
       <c r="L41" s="8" t="inlineStr"/>
       <c r="M41" s="9" t="inlineStr">
         <is>
-          <t>dundalk leisurecraft sauna</t>
+          <t>scandia sauna heater</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr"/>
@@ -3662,7 +3666,11 @@
       <c r="Q41" s="9" t="inlineStr"/>
       <c r="R41" s="9" t="inlineStr"/>
       <c r="S41" s="9" t="inlineStr"/>
-      <c r="T41" s="7" t="inlineStr"/>
+      <c r="T41" s="7" t="inlineStr">
+        <is>
+          <t>Duplicate of /scandia (9 products). | NOT merged, 7 September 2026. The product diff overrode the merge instruction: zero overlap. scandia holds 9 cabins and kits $9,450-$14,800; scandia-manufacturing holds 10 heaters $1,300-$6,200, and draws 189 GSC impressions to scandia's 28. Merging would have buried the collection people actually find. Renamed for clarity instead - TITLES ONLY, handles unchanged, because a handle change needs a 301 and scandia-manufacturing is the one carrying traffic.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -3670,24 +3678,24 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>scandia-manufacturing</t>
+          <t>spa</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/scandia-manufacturing</t>
+          <t>https://inhousewellness.com/collections/spa</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Scandia Manufacturing</t>
+          <t>Spa</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -3711,13 +3719,13 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>MERGE?</t>
+          <t>WRITE</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr"/>
       <c r="M42" s="9" t="inlineStr">
         <is>
-          <t>scandia sauna</t>
+          <t>home spa</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr"/>
@@ -3726,11 +3734,7 @@
       <c r="Q42" s="9" t="inlineStr"/>
       <c r="R42" s="9" t="inlineStr"/>
       <c r="S42" s="9" t="inlineStr"/>
-      <c r="T42" s="7" t="inlineStr">
-        <is>
-          <t>Duplicate of /scandia (9 products).</t>
-        </is>
-      </c>
+      <c r="T42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -3738,21 +3742,21 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>spa</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/spa</t>
+          <t>https://inhousewellness.com/collections/frozen</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Spa</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>0</v>
@@ -3764,7 +3768,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -3774,7 +3778,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -3785,7 +3789,7 @@
       <c r="L43" s="8" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>home spa</t>
+          <t>frozen cold plunge</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr"/>
@@ -3794,7 +3798,11 @@
       <c r="Q43" s="9" t="inlineStr"/>
       <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="9" t="inlineStr"/>
-      <c r="T43" s="7" t="inlineStr"/>
+      <c r="T43" s="7" t="inlineStr">
+        <is>
+          <t>One of the few decent descriptions. | Description cleared 2026-09-07: contained health claims that would have become visible when the theme render fix ships. Needs new copy.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -3802,24 +3810,24 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>scandia</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/frozen</t>
+          <t>https://inhousewellness.com/collections/scandia</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Scandia Saunas</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
         <v>9</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
@@ -3828,7 +3836,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -3838,7 +3846,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -3849,7 +3857,7 @@
       <c r="L44" s="8" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>frozen cold plunge</t>
+          <t>scandia sauna</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr"/>
@@ -3860,7 +3868,7 @@
       <c r="S44" s="9" t="inlineStr"/>
       <c r="T44" s="7" t="inlineStr">
         <is>
-          <t>One of the few decent descriptions. | Description cleared 2026-09-07: contained health claims that would have become visible when the theme render fix ships. Needs new copy.</t>
+          <t>Duplicate of /scandia-manufacturing. | NOT merged, 7 September 2026. The product diff overrode the merge instruction: zero overlap. scandia holds 9 cabins and kits $9,450-$14,800; scandia-manufacturing holds 10 heaters $1,300-$6,200, and draws 189 GSC impressions to scandia's 28. Merging would have buried the collection people actually find. Renamed for clarity instead - TITLES ONLY, handles unchanged, because a handle change needs a 301 and scandia-manufacturing is the one carrying traffic.</t>
         </is>
       </c>
     </row>
@@ -3870,24 +3878,24 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>scandia</t>
+          <t>chimneys</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/scandia</t>
+          <t>https://inhousewellness.com/collections/chimneys</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Scandia</t>
+          <t>Chimneys</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
@@ -3911,13 +3919,13 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>MERGE?</t>
+          <t>WRITE</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr"/>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>scandia sauna</t>
+          <t>sauna chimney kit</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr"/>
@@ -3926,11 +3934,7 @@
       <c r="Q45" s="9" t="inlineStr"/>
       <c r="R45" s="9" t="inlineStr"/>
       <c r="S45" s="9" t="inlineStr"/>
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>Duplicate of /scandia-manufacturing.</t>
-        </is>
-      </c>
+      <c r="T45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -3938,24 +3942,24 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>chimneys</t>
+          <t>chimney-option</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/chimneys</t>
+          <t>https://inhousewellness.com/collections/chimney-option</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Chimneys</t>
+          <t>Chimney Option</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
         <v>8</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
@@ -3979,22 +3983,22 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>WRITE</t>
+          <t>MERGE?</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>sauna chimney kit</t>
-        </is>
-      </c>
+      <c r="M46" s="9" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="8" t="inlineStr"/>
       <c r="P46" s="8" t="inlineStr"/>
       <c r="Q46" s="9" t="inlineStr"/>
       <c r="R46" s="9" t="inlineStr"/>
       <c r="S46" s="9" t="inlineStr"/>
-      <c r="T46" s="7" t="inlineStr"/>
+      <c r="T46" s="7" t="inlineStr">
+        <is>
+          <t>Near-duplicate of /chimneys, same 8 products?</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -4002,24 +4006,24 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>chimney-option</t>
+          <t>medical-breakthrough</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/chimney-option</t>
+          <t>https://inhousewellness.com/collections/medical-breakthrough</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Chimney Option</t>
+          <t>Medical Breakthrough</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -4028,7 +4032,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -4038,27 +4042,27 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>MERGE?</t>
+          <t>WRITE</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>medical breakthrough massage chair</t>
+        </is>
+      </c>
       <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="8" t="inlineStr"/>
       <c r="P47" s="8" t="inlineStr"/>
       <c r="Q47" s="9" t="inlineStr"/>
       <c r="R47" s="9" t="inlineStr"/>
       <c r="S47" s="9" t="inlineStr"/>
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>Near-duplicate of /chimneys, same 8 products?</t>
-        </is>
-      </c>
+      <c r="T47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -4066,24 +4070,24 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>medical-breakthrough</t>
+          <t>hot-tubs</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/medical-breakthrough</t>
+          <t>https://inhousewellness.com/collections/hot-tubs</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Medical Breakthrough</t>
+          <t>Hot Tubs</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
         <v>7</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -4113,7 +4117,7 @@
       <c r="L48" s="8" t="inlineStr"/>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>medical breakthrough massage chair</t>
+          <t>hot tub</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr"/>
@@ -4130,24 +4134,24 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>hot-tubs</t>
+          <t>kahuna-chair</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/hot-tubs</t>
+          <t>https://inhousewellness.com/collections/kahuna-chair</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Hot Tubs</t>
+          <t>Kahuna Chair</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -4156,7 +4160,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -4166,7 +4170,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -4177,7 +4181,7 @@
       <c r="L49" s="8" t="inlineStr"/>
       <c r="M49" s="9" t="inlineStr">
         <is>
-          <t>hot tub</t>
+          <t>kahuna massage chair</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr"/>
@@ -4194,24 +4198,24 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>kahuna-chair</t>
+          <t>finnmark-designs</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/kahuna-chair</t>
+          <t>https://inhousewellness.com/collections/finnmark-designs</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Kahuna Chair</t>
+          <t>Finnmark Designs</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
         <v>6</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -4241,7 +4245,7 @@
       <c r="L50" s="8" t="inlineStr"/>
       <c r="M50" s="9" t="inlineStr">
         <is>
-          <t>kahuna massage chair</t>
+          <t>finnmark sauna</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr"/>
@@ -4250,7 +4254,11 @@
       <c r="Q50" s="9" t="inlineStr"/>
       <c r="R50" s="9" t="inlineStr"/>
       <c r="S50" s="9" t="inlineStr"/>
-      <c r="T50" s="7" t="inlineStr"/>
+      <c r="T50" s="7" t="inlineStr">
+        <is>
+          <t>Product titles truncate on homepage ('Finnmar…').</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -4258,24 +4266,24 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>finnmark-designs</t>
+          <t>mr-steam</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/finnmark-designs</t>
+          <t>https://inhousewellness.com/collections/mr-steam</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Finnmark Designs</t>
+          <t>Mr. Steam</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -4305,7 +4313,7 @@
       <c r="L51" s="8" t="inlineStr"/>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>finnmark sauna</t>
+          <t>mr steam</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr"/>
@@ -4314,11 +4322,7 @@
       <c r="Q51" s="9" t="inlineStr"/>
       <c r="R51" s="9" t="inlineStr"/>
       <c r="S51" s="9" t="inlineStr"/>
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>Product titles truncate on homepage ('Finnmar…').</t>
-        </is>
-      </c>
+      <c r="T51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -4326,24 +4330,24 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>mr-steam</t>
+          <t>roof-option</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/mr-steam</t>
+          <t>https://inhousewellness.com/collections/roof-option</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Mr. Steam</t>
+          <t>Roof Option</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -4373,7 +4377,7 @@
       <c r="L52" s="8" t="inlineStr"/>
       <c r="M52" s="9" t="inlineStr">
         <is>
-          <t>mr steam</t>
+          <t>sauna roof</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr"/>
@@ -4390,21 +4394,21 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>roof-option</t>
+          <t>cabin-sauna</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/roof-option</t>
+          <t>https://inhousewellness.com/collections/cabin-sauna</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Roof Option</t>
+          <t>Cabin Sauna</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>0</v>
@@ -4437,7 +4441,7 @@
       <c r="L53" s="8" t="inlineStr"/>
       <c r="M53" s="9" t="inlineStr">
         <is>
-          <t>sauna roof</t>
+          <t>cabin sauna</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr"/>
@@ -4446,7 +4450,11 @@
       <c r="Q53" s="9" t="inlineStr"/>
       <c r="R53" s="9" t="inlineStr"/>
       <c r="S53" s="9" t="inlineStr"/>
-      <c r="T53" s="7" t="inlineStr"/>
+      <c r="T53" s="7" t="inlineStr">
+        <is>
+          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -4454,24 +4462,24 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>cabin-sauna</t>
+          <t>designer-sauna-heaters</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/cabin-sauna</t>
+          <t>https://inhousewellness.com/collections/designer-sauna-heaters</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Cabin Sauna</t>
+          <t>Designer Sauna Heaters</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -4485,14 +4493,10 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr"/>
       <c r="K54" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -4501,7 +4505,7 @@
       <c r="L54" s="8" t="inlineStr"/>
       <c r="M54" s="9" t="inlineStr">
         <is>
-          <t>cabin sauna</t>
+          <t>designer sauna heater</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr"/>
@@ -4510,11 +4514,7 @@
       <c r="Q54" s="9" t="inlineStr"/>
       <c r="R54" s="9" t="inlineStr"/>
       <c r="S54" s="9" t="inlineStr"/>
-      <c r="T54" s="7" t="inlineStr">
-        <is>
-          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
-        </is>
-      </c>
+      <c r="T54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -4522,24 +4522,24 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>designer-sauna-heaters</t>
+          <t>service-upgrades</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/designer-sauna-heaters</t>
+          <t>https://inhousewellness.com/collections/service-upgrades</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Designer Sauna Heaters</t>
+          <t>Service Upgrades</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -4553,10 +4553,14 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -4565,7 +4569,7 @@
       <c r="L55" s="8" t="inlineStr"/>
       <c r="M55" s="9" t="inlineStr">
         <is>
-          <t>designer sauna heater</t>
+          <t>sauna installation service</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr"/>
@@ -4574,7 +4578,11 @@
       <c r="Q55" s="9" t="inlineStr"/>
       <c r="R55" s="9" t="inlineStr"/>
       <c r="S55" s="9" t="inlineStr"/>
-      <c r="T55" s="7" t="inlineStr"/>
+      <c r="T55" s="7" t="inlineStr">
+        <is>
+          <t>Ties to the True Total Cost tool.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -4582,24 +4590,24 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>service-upgrades</t>
+          <t>cal-saunas</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/service-upgrades</t>
+          <t>https://inhousewellness.com/collections/cal-saunas</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Service Upgrades</t>
+          <t>Cal Saunas</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -4608,7 +4616,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -4618,7 +4626,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -4629,7 +4637,7 @@
       <c r="L56" s="8" t="inlineStr"/>
       <c r="M56" s="9" t="inlineStr">
         <is>
-          <t>sauna installation service</t>
+          <t>cal saunas</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr"/>
@@ -4638,11 +4646,7 @@
       <c r="Q56" s="9" t="inlineStr"/>
       <c r="R56" s="9" t="inlineStr"/>
       <c r="S56" s="9" t="inlineStr"/>
-      <c r="T56" s="7" t="inlineStr">
-        <is>
-          <t>Ties to the True Total Cost tool.</t>
-        </is>
-      </c>
+      <c r="T56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -4650,24 +4654,24 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>cal-saunas</t>
+          <t>mande-spa</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/cal-saunas</t>
+          <t>https://inhousewellness.com/collections/mande-spa</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Cal Saunas</t>
+          <t>Mande Spa</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -4676,19 +4680,15 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>title + meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr"/>
       <c r="K57" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -4697,7 +4697,7 @@
       <c r="L57" s="8" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr">
         <is>
-          <t>cal saunas</t>
+          <t>mande spa</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr"/>
@@ -4714,21 +4714,21 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>mande-spa</t>
+          <t>health-smart</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/mande-spa</t>
+          <t>https://inhousewellness.com/collections/health-smart</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Mande Spa</t>
+          <t>Health Smart</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>0</v>
@@ -4755,11 +4755,7 @@
         </is>
       </c>
       <c r="L58" s="8" t="inlineStr"/>
-      <c r="M58" s="9" t="inlineStr">
-        <is>
-          <t>mande spa</t>
-        </is>
-      </c>
+      <c r="M58" s="9" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="8" t="inlineStr"/>
       <c r="P58" s="8" t="inlineStr"/>
@@ -4774,24 +4770,24 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>health-smart</t>
+          <t>ripavi</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/health-smart</t>
+          <t>https://inhousewellness.com/collections/ripavi</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Health Smart</t>
+          <t>Ripavi</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -4800,22 +4796,30 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>title + meta</t>
+        </is>
+      </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr"/>
-      <c r="M59" s="9" t="inlineStr"/>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>ripavi sauna</t>
+        </is>
+      </c>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="8" t="inlineStr"/>
       <c r="P59" s="8" t="inlineStr"/>
@@ -4830,24 +4834,24 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>ripavi</t>
+          <t>float-tank-upgrades</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/ripavi</t>
+          <t>https://inhousewellness.com/collections/float-tank-upgrades</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Ripavi</t>
+          <t>Float Tank Upgrades</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -4856,7 +4860,7 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
@@ -4866,7 +4870,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -4877,7 +4881,7 @@
       <c r="L60" s="8" t="inlineStr"/>
       <c r="M60" s="9" t="inlineStr">
         <is>
-          <t>ripavi sauna</t>
+          <t>float tank accessories</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr"/>
@@ -4894,24 +4898,24 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>float-tank-upgrades</t>
+          <t>sauna-maintenance-product</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/float-tank-upgrades</t>
+          <t>https://inhousewellness.com/collections/sauna-maintenance-product</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Float Tank Upgrades</t>
+          <t>Sauna Maintenance Product</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -4941,7 +4945,7 @@
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr">
         <is>
-          <t>float tank accessories</t>
+          <t>sauna maintenance</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr"/>
@@ -4958,24 +4962,24 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>sauna-maintenance-product</t>
+          <t>electric-saunas</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/sauna-maintenance-product</t>
+          <t>https://inhousewellness.com/collections/electric-saunas</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Sauna Maintenance Product</t>
+          <t>Electric Saunas</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
@@ -4984,7 +4988,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -4994,7 +4998,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -5005,7 +5009,7 @@
       <c r="L62" s="8" t="inlineStr"/>
       <c r="M62" s="9" t="inlineStr">
         <is>
-          <t>sauna maintenance</t>
+          <t>electric sauna</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr"/>
@@ -5022,24 +5026,24 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>electric-saunas</t>
+          <t>helios-massage-chair</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/electric-saunas</t>
+          <t>https://inhousewellness.com/collections/helios-massage-chair</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Electric Saunas</t>
+          <t>Helios Massage Chair</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -5048,19 +5052,15 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr">
-        <is>
-          <t>title + meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr"/>
       <c r="K63" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -5069,7 +5069,7 @@
       <c r="L63" s="8" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr">
         <is>
-          <t>electric sauna</t>
+          <t>helios massage chair</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr"/>
@@ -5086,24 +5086,24 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>helios-massage-chair</t>
+          <t>heater-floor-plate</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/helios-massage-chair</t>
+          <t>https://inhousewellness.com/collections/heater-floor-plate</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Helios Massage Chair</t>
+          <t>Heater Floor Plate</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
@@ -5117,10 +5117,14 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -5129,7 +5133,7 @@
       <c r="L64" s="8" t="inlineStr"/>
       <c r="M64" s="9" t="inlineStr">
         <is>
-          <t>helios massage chair</t>
+          <t>sauna heater floor plate</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr"/>
@@ -5146,24 +5150,24 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>heater-floor-plate</t>
+          <t>leisurecraft-cold-plunge</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/heater-floor-plate</t>
+          <t>https://inhousewellness.com/collections/leisurecraft-cold-plunge</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Heater Floor Plate</t>
+          <t>LeisureCraft Cold Plunge</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -5193,7 +5197,7 @@
       <c r="L65" s="8" t="inlineStr"/>
       <c r="M65" s="9" t="inlineStr">
         <is>
-          <t>sauna heater floor plate</t>
+          <t>dundalk cold plunge</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr"/>
@@ -5210,24 +5214,24 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>leisurecraft-cold-plunge</t>
+          <t>cold-plunge-accessories</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/leisurecraft-cold-plunge</t>
+          <t>https://inhousewellness.com/collections/cold-plunge-accessories</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>LeisureCraft Cold Plunge</t>
+          <t>Cold Plunge Accessories</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
@@ -5241,14 +5245,10 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr"/>
       <c r="K66" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -5257,7 +5257,7 @@
       <c r="L66" s="8" t="inlineStr"/>
       <c r="M66" s="9" t="inlineStr">
         <is>
-          <t>dundalk cold plunge</t>
+          <t>cold plunge accessories</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr"/>
@@ -5274,17 +5274,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>cold-plunge-accessories</t>
+          <t>dynamic-cold-therapy-accesories</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/cold-plunge-accessories</t>
+          <t>https://inhousewellness.com/collections/dynamic-cold-therapy-accesories</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Cold Plunge Accessories</t>
+          <t>Dynamic Cold Therapy Accesories</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
@@ -5315,81 +5315,21 @@
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr"/>
-      <c r="M67" s="9" t="inlineStr">
-        <is>
-          <t>cold plunge accessories</t>
-        </is>
-      </c>
+      <c r="M67" s="9" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="8" t="inlineStr"/>
       <c r="P67" s="8" t="inlineStr"/>
       <c r="Q67" s="9" t="inlineStr"/>
       <c r="R67" s="9" t="inlineStr"/>
       <c r="S67" s="9" t="inlineStr"/>
-      <c r="T67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>dynamic-cold-therapy-accesories</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>https://inhousewellness.com/collections/dynamic-cold-therapy-accesories</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Dynamic Cold Therapy Accesories</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>empty</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" s="6" t="inlineStr">
-        <is>
-          <t>WRITE</t>
-        </is>
-      </c>
-      <c r="L68" s="8" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="8" t="inlineStr"/>
-      <c r="P68" s="8" t="inlineStr"/>
-      <c r="Q68" s="9" t="inlineStr"/>
-      <c r="R68" s="9" t="inlineStr"/>
-      <c r="S68" s="9" t="inlineStr"/>
-      <c r="T68" s="7" t="inlineStr">
+      <c r="T67" s="7" t="inlineStr">
         <is>
           <t>Typo in handle: 'Accesories'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T68"/>
+  <autoFilter ref="A1:T67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5750,14 +5690,14 @@
           <t>newest-products, best-selling-products</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>YOU DECIDE</t>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Both still published, both ~673 products. best-selling-products top-20 dropped for the season (BACKLOG B9).</t>
+          <t>newest-products unpublished 7 Sept - /collections/all covers it. Verified zero references across 559 theme files and 210 nav items first. best-selling-products kept.</t>
         </is>
       </c>
     </row>
@@ -5777,14 +5717,14 @@
           <t>low-emf / ultra-low-emf / near-zero-emf</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>YOU DECIDE</t>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>DECIDED</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Confirm low-emf as the hub. Highest-CPC cluster in the store, $9.15-$30.02.</t>
+          <t>All three stay as siblings with distinct keywords. Hub-and-spoke plan dropped - they are different products for different buyers, not one thing split three ways.</t>
         </is>
       </c>
     </row>
@@ -5804,14 +5744,14 @@
           <t>2 collections, 19 products</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>YOU DECIDE</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>DECIDED</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>NOT a duplicate pair - zero product overlap. scandia is 9 cabins/kits $9,450-$14,800; scandia-manufacturing is 10 heaters $1,300-$6,200. Recommend renaming, not merging.</t>
+          <t>NOT merged. Zero product overlap - 9 cabins vs 10 heaters, and scandia-manufacturing draws 189 impressions to scandia's 28. Renamed for clarity, titles only, handles unchanged.</t>
         </is>
       </c>
     </row>
@@ -5831,14 +5771,14 @@
           <t>2 collections, 7 products</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>YOU DECIDE</t>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>AWAITING YOU</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>TRUE duplicate - identical membership, all 7 products in both. One should go. Neither draws traffic (0 and 1 impressions).</t>
+          <t>True duplicate, all 8 products in both. Merge is: unpublish chimney-option + 301 to chimneys. No products move. Diff shown, nothing moved yet.</t>
         </is>
       </c>
     </row>

--- a/inh-seo/docs/collection-worksheet.xlsx
+++ b/inh-seo/docs/collection-worksheet.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Mechanical Fixes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Collections'!$A$1:$T$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Collections'!$A$1:$T$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  66 collections are in this worksheet.</t>
+          <t xml:space="preserve">  68 collections are in this worksheet.</t>
         </is>
       </c>
     </row>
@@ -546,21 +546,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs a NEW SEO TITLE:        53 of 66   (13 already have one — leave those blank)</t>
+          <t xml:space="preserve">  Needs a NEW SEO TITLE:        55 of 68   (13 already have one — leave those blank)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs a NEW META DESCRIPTION: 15 of 66   (51 already have one)</t>
+          <t xml:space="preserve">  Needs a NEW META DESCRIPTION: 17 of 68   (51 already have one)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs a DESCRIPTION:          63 of 66   (3 already written)</t>
+          <t xml:space="preserve">  Needs a DESCRIPTION:          58 of 68   (10 already written)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  24 rows were dropped from the 90-collection plan:</t>
+          <t xml:space="preserve">  22 rows were dropped from the 90-collection plan:</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11 marked SCOPE-OUT — outdoor cooking, a deliberate decision, not a gap</t>
+          <t xml:space="preserve">     9 marked SCOPE-OUT — outdoor cooking, a deliberate decision, not a gap</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  19 of 66 collections got ZERO. Total across all rows: 2,778 impressions, 5 clicks.</t>
+          <t xml:space="preserve">  20 of 68 collections got ZERO. Total across all rows: 2,788 impressions, 5 clicks.</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T67"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>has copy</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>meta + description</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>has copy</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>meta + description</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>has copy</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>meta + description</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>has copy</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>meta + description</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>has copy</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>meta + description</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>has copy</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>meta + description</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>has copy</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1758,7 +1758,11 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -4134,24 +4138,24 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>kahuna-chair</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/kahuna-chair</t>
+          <t>https://inhousewellness.com/collections/delta</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Kahuna Chair</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -4165,32 +4169,28 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr"/>
       <c r="K49" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr"/>
-      <c r="M49" s="9" t="inlineStr">
-        <is>
-          <t>kahuna massage chair</t>
-        </is>
-      </c>
+      <c r="M49" s="9" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="8" t="inlineStr"/>
       <c r="P49" s="8" t="inlineStr"/>
       <c r="Q49" s="9" t="inlineStr"/>
       <c r="R49" s="9" t="inlineStr"/>
       <c r="S49" s="9" t="inlineStr"/>
-      <c r="T49" s="7" t="inlineStr"/>
+      <c r="T49" s="7" t="inlineStr">
+        <is>
+          <t>No SEO fields. Unclear what this is. | SCOPE-OUT 7 September 2026, client decision. Outdoor cooking is deliberately outside the SEO programme but stays IN the catalogue: published, sellable, indexed. It draws some inquiries and little revenue, so it does not earn copywriting hours against a 15 November deadline. This is a decision, not an oversight - do not treat the absence of descriptions here as a gap to fill. | SCOPE-OUT REVERSED 7 September 2026. This collection was included in the client's list of 11 outdoor-cooking collections, but it is not outdoor cooking. Found by auditing the 11 by product TITLE rather than by collection name. Returned to the sweep.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -4198,24 +4198,24 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>finnmark-designs</t>
+          <t>kahuna-chair</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/finnmark-designs</t>
+          <t>https://inhousewellness.com/collections/kahuna-chair</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Finnmark Designs</t>
+          <t>Kahuna Chair</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
         <v>6</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       <c r="L50" s="8" t="inlineStr"/>
       <c r="M50" s="9" t="inlineStr">
         <is>
-          <t>finnmark sauna</t>
+          <t>kahuna massage chair</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr"/>
@@ -4254,11 +4254,7 @@
       <c r="Q50" s="9" t="inlineStr"/>
       <c r="R50" s="9" t="inlineStr"/>
       <c r="S50" s="9" t="inlineStr"/>
-      <c r="T50" s="7" t="inlineStr">
-        <is>
-          <t>Product titles truncate on homepage ('Finnmar…').</t>
-        </is>
-      </c>
+      <c r="T50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -4266,24 +4262,24 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>mr-steam</t>
+          <t>finnmark-designs</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/mr-steam</t>
+          <t>https://inhousewellness.com/collections/finnmark-designs</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Mr. Steam</t>
+          <t>Finnmark Designs</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -4313,7 +4309,7 @@
       <c r="L51" s="8" t="inlineStr"/>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>mr steam</t>
+          <t>finnmark sauna</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr"/>
@@ -4322,7 +4318,11 @@
       <c r="Q51" s="9" t="inlineStr"/>
       <c r="R51" s="9" t="inlineStr"/>
       <c r="S51" s="9" t="inlineStr"/>
-      <c r="T51" s="7" t="inlineStr"/>
+      <c r="T51" s="7" t="inlineStr">
+        <is>
+          <t>Product titles truncate on homepage ('Finnmar…').</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -4330,24 +4330,24 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>roof-option</t>
+          <t>mr-steam</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/roof-option</t>
+          <t>https://inhousewellness.com/collections/mr-steam</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Roof Option</t>
+          <t>Mr. Steam</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
       <c r="L52" s="8" t="inlineStr"/>
       <c r="M52" s="9" t="inlineStr">
         <is>
-          <t>sauna roof</t>
+          <t>mr steam</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr"/>
@@ -4394,21 +4394,21 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>cabin-sauna</t>
+          <t>roof-option</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/cabin-sauna</t>
+          <t>https://inhousewellness.com/collections/roof-option</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Cabin Sauna</t>
+          <t>Roof Option</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
       <c r="L53" s="8" t="inlineStr"/>
       <c r="M53" s="9" t="inlineStr">
         <is>
-          <t>cabin sauna</t>
+          <t>sauna roof</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr"/>
@@ -4450,11 +4450,7 @@
       <c r="Q53" s="9" t="inlineStr"/>
       <c r="R53" s="9" t="inlineStr"/>
       <c r="S53" s="9" t="inlineStr"/>
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
-        </is>
-      </c>
+      <c r="T53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -4462,24 +4458,24 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>designer-sauna-heaters</t>
+          <t>cabin-sauna</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/designer-sauna-heaters</t>
+          <t>https://inhousewellness.com/collections/cabin-sauna</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Designer Sauna Heaters</t>
+          <t>Cabin Sauna</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -4493,10 +4489,14 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -4505,7 +4505,7 @@
       <c r="L54" s="8" t="inlineStr"/>
       <c r="M54" s="9" t="inlineStr">
         <is>
-          <t>designer sauna heater</t>
+          <t>cabin sauna</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr"/>
@@ -4514,7 +4514,11 @@
       <c r="Q54" s="9" t="inlineStr"/>
       <c r="R54" s="9" t="inlineStr"/>
       <c r="S54" s="9" t="inlineStr"/>
-      <c r="T54" s="7" t="inlineStr"/>
+      <c r="T54" s="7" t="inlineStr">
+        <is>
+          <t>Meta rewritten 2026-09-07: removed health-claim language before the theme render fix made it public. Built from products.json.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -4522,24 +4526,24 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>service-upgrades</t>
+          <t>designer-sauna-heaters</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/service-upgrades</t>
+          <t>https://inhousewellness.com/collections/designer-sauna-heaters</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Service Upgrades</t>
+          <t>Designer Sauna Heaters</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -4553,14 +4557,10 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr"/>
       <c r="K55" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -4569,7 +4569,7 @@
       <c r="L55" s="8" t="inlineStr"/>
       <c r="M55" s="9" t="inlineStr">
         <is>
-          <t>sauna installation service</t>
+          <t>designer sauna heater</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr"/>
@@ -4578,11 +4578,7 @@
       <c r="Q55" s="9" t="inlineStr"/>
       <c r="R55" s="9" t="inlineStr"/>
       <c r="S55" s="9" t="inlineStr"/>
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>Ties to the True Total Cost tool.</t>
-        </is>
-      </c>
+      <c r="T55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -4590,24 +4586,24 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>cal-saunas</t>
+          <t>service-upgrades</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/cal-saunas</t>
+          <t>https://inhousewellness.com/collections/service-upgrades</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Cal Saunas</t>
+          <t>Service Upgrades</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -4616,7 +4612,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -4626,7 +4622,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -4637,7 +4633,7 @@
       <c r="L56" s="8" t="inlineStr"/>
       <c r="M56" s="9" t="inlineStr">
         <is>
-          <t>cal saunas</t>
+          <t>sauna installation service</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr"/>
@@ -4646,7 +4642,11 @@
       <c r="Q56" s="9" t="inlineStr"/>
       <c r="R56" s="9" t="inlineStr"/>
       <c r="S56" s="9" t="inlineStr"/>
-      <c r="T56" s="7" t="inlineStr"/>
+      <c r="T56" s="7" t="inlineStr">
+        <is>
+          <t>Ties to the True Total Cost tool.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -4654,24 +4654,24 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>mande-spa</t>
+          <t>cal-saunas</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/mande-spa</t>
+          <t>https://inhousewellness.com/collections/cal-saunas</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Mande Spa</t>
+          <t>Cal Saunas</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -4680,15 +4680,19 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>title + meta</t>
+        </is>
+      </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -4697,7 +4701,7 @@
       <c r="L57" s="8" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr">
         <is>
-          <t>mande spa</t>
+          <t>cal saunas</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr"/>
@@ -4714,21 +4718,21 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>health-smart</t>
+          <t>mande-spa</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/health-smart</t>
+          <t>https://inhousewellness.com/collections/mande-spa</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Health Smart</t>
+          <t>Mande Spa</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>0</v>
@@ -4755,7 +4759,11 @@
         </is>
       </c>
       <c r="L58" s="8" t="inlineStr"/>
-      <c r="M58" s="9" t="inlineStr"/>
+      <c r="M58" s="9" t="inlineStr">
+        <is>
+          <t>mande spa</t>
+        </is>
+      </c>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="8" t="inlineStr"/>
       <c r="P58" s="8" t="inlineStr"/>
@@ -4770,24 +4778,24 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>ripavi</t>
+          <t>health-smart</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/ripavi</t>
+          <t>https://inhousewellness.com/collections/health-smart</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Ripavi</t>
+          <t>Health Smart</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -4796,30 +4804,22 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>title + meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr"/>
       <c r="K59" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr"/>
-      <c r="M59" s="9" t="inlineStr">
-        <is>
-          <t>ripavi sauna</t>
-        </is>
-      </c>
+      <c r="M59" s="9" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="8" t="inlineStr"/>
       <c r="P59" s="8" t="inlineStr"/>
@@ -4834,24 +4834,24 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>float-tank-upgrades</t>
+          <t>ripavi</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/float-tank-upgrades</t>
+          <t>https://inhousewellness.com/collections/ripavi</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Float Tank Upgrades</t>
+          <t>Ripavi</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>title + meta</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -4881,7 +4881,7 @@
       <c r="L60" s="8" t="inlineStr"/>
       <c r="M60" s="9" t="inlineStr">
         <is>
-          <t>float tank accessories</t>
+          <t>ripavi sauna</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr"/>
@@ -4898,24 +4898,24 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>sauna-maintenance-product</t>
+          <t>float-tank-upgrades</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/sauna-maintenance-product</t>
+          <t>https://inhousewellness.com/collections/float-tank-upgrades</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Sauna Maintenance Product</t>
+          <t>Float Tank Upgrades</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr">
         <is>
-          <t>sauna maintenance</t>
+          <t>float tank accessories</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr"/>
@@ -4962,24 +4962,24 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>electric-saunas</t>
+          <t>sauna-maintenance-product</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/electric-saunas</t>
+          <t>https://inhousewellness.com/collections/sauna-maintenance-product</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Electric Saunas</t>
+          <t>Sauna Maintenance Product</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>title + meta</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -5009,7 +5009,7 @@
       <c r="L62" s="8" t="inlineStr"/>
       <c r="M62" s="9" t="inlineStr">
         <is>
-          <t>electric sauna</t>
+          <t>sauna maintenance</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr"/>
@@ -5026,24 +5026,24 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>helios-massage-chair</t>
+          <t>electric-saunas</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/helios-massage-chair</t>
+          <t>https://inhousewellness.com/collections/electric-saunas</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Helios Massage Chair</t>
+          <t>Electric Saunas</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -5052,15 +5052,19 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>title + meta</t>
+        </is>
+      </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -5069,7 +5073,7 @@
       <c r="L63" s="8" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr">
         <is>
-          <t>helios massage chair</t>
+          <t>electric sauna</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr"/>
@@ -5086,21 +5090,21 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>heater-floor-plate</t>
+          <t>kohler</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/heater-floor-plate</t>
+          <t>https://inhousewellness.com/collections/kohler</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Heater Floor Plate</t>
+          <t>Kohler</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>0</v>
@@ -5117,32 +5121,28 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr"/>
       <c r="K64" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
         </is>
       </c>
       <c r="L64" s="8" t="inlineStr"/>
-      <c r="M64" s="9" t="inlineStr">
-        <is>
-          <t>sauna heater floor plate</t>
-        </is>
-      </c>
+      <c r="M64" s="9" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="8" t="inlineStr"/>
       <c r="P64" s="8" t="inlineStr"/>
       <c r="Q64" s="9" t="inlineStr"/>
       <c r="R64" s="9" t="inlineStr"/>
       <c r="S64" s="9" t="inlineStr"/>
-      <c r="T64" s="7" t="inlineStr"/>
+      <c r="T64" s="7" t="inlineStr">
+        <is>
+          <t>SCOPE-OUT 7 September 2026, client decision. Outdoor cooking is deliberately outside the SEO programme but stays IN the catalogue: published, sellable, indexed. It draws some inquiries and little revenue, so it does not earn copywriting hours against a 15 November deadline. This is a decision, not an oversight - do not treat the absence of descriptions here as a gap to fill. | SCOPE-OUT REVERSED 7 September 2026. This collection was included in the client's list of 11 outdoor-cooking collections, but it is not outdoor cooking. Found by auditing the 11 by product TITLE rather than by collection name. Returned to the sweep.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -5150,24 +5150,24 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>leisurecraft-cold-plunge</t>
+          <t>helios-massage-chair</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/leisurecraft-cold-plunge</t>
+          <t>https://inhousewellness.com/collections/helios-massage-chair</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>LeisureCraft Cold Plunge</t>
+          <t>Helios Massage Chair</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -5181,14 +5181,10 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr"/>
       <c r="K65" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -5197,7 +5193,7 @@
       <c r="L65" s="8" t="inlineStr"/>
       <c r="M65" s="9" t="inlineStr">
         <is>
-          <t>dundalk cold plunge</t>
+          <t>helios massage chair</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr"/>
@@ -5214,17 +5210,17 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>cold-plunge-accessories</t>
+          <t>heater-floor-plate</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/cold-plunge-accessories</t>
+          <t>https://inhousewellness.com/collections/heater-floor-plate</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Cold Plunge Accessories</t>
+          <t>Heater Floor Plate</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
@@ -5245,10 +5241,14 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
@@ -5257,7 +5257,7 @@
       <c r="L66" s="8" t="inlineStr"/>
       <c r="M66" s="9" t="inlineStr">
         <is>
-          <t>cold plunge accessories</t>
+          <t>sauna heater floor plate</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr"/>
@@ -5274,24 +5274,24 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>dynamic-cold-therapy-accesories</t>
+          <t>leisurecraft-cold-plunge</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>https://inhousewellness.com/collections/dynamic-cold-therapy-accesories</t>
+          <t>https://inhousewellness.com/collections/leisurecraft-cold-plunge</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Dynamic Cold Therapy Accesories</t>
+          <t>LeisureCraft Cold Plunge</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
@@ -5305,31 +5305,155 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
           <t>WRITE</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr"/>
-      <c r="M67" s="9" t="inlineStr"/>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>dundalk cold plunge</t>
+        </is>
+      </c>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="8" t="inlineStr"/>
       <c r="P67" s="8" t="inlineStr"/>
       <c r="Q67" s="9" t="inlineStr"/>
       <c r="R67" s="9" t="inlineStr"/>
       <c r="S67" s="9" t="inlineStr"/>
-      <c r="T67" s="7" t="inlineStr">
+      <c r="T67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>cold-plunge-accessories</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>https://inhousewellness.com/collections/cold-plunge-accessories</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Cold Plunge Accessories</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>WRITE</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>cold plunge accessories</t>
+        </is>
+      </c>
+      <c r="N68" s="8" t="inlineStr"/>
+      <c r="O68" s="8" t="inlineStr"/>
+      <c r="P68" s="8" t="inlineStr"/>
+      <c r="Q68" s="9" t="inlineStr"/>
+      <c r="R68" s="9" t="inlineStr"/>
+      <c r="S68" s="9" t="inlineStr"/>
+      <c r="T68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>dynamic-cold-therapy-accesories</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>https://inhousewellness.com/collections/dynamic-cold-therapy-accesories</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Dynamic Cold Therapy Accesories</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>WRITE</t>
+        </is>
+      </c>
+      <c r="L69" s="8" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="8" t="inlineStr"/>
+      <c r="O69" s="8" t="inlineStr"/>
+      <c r="P69" s="8" t="inlineStr"/>
+      <c r="Q69" s="9" t="inlineStr"/>
+      <c r="R69" s="9" t="inlineStr"/>
+      <c r="S69" s="9" t="inlineStr"/>
+      <c r="T69" s="7" t="inlineStr">
         <is>
           <t>Typo in handle: 'Accesories'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T67"/>
+  <autoFilter ref="A1:T69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5340,7 +5464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5692,12 +5816,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>PARTLY DONE</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>newest-products unpublished 7 Sept - /collections/all covers it. Verified zero references across 559 theme files and 210 nav items first. best-selling-products kept.</t>
+          <t>newest-products unpublished 7 Sept. BUT best-selling-products has the IDENTICAL tautological rule - TITLE CONTAINS "Best Selling" OR TITLE NOT_CONTAINS "Best Selling", applied OR - so it also holds all 673 products and does not list best sellers. The survivor needs a real rule or a different purpose. Reopened.</t>
         </is>
       </c>
     </row>
@@ -5773,12 +5897,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>AWAITING YOU</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>True duplicate, all 8 products in both. Merge is: unpublish chimney-option + 301 to chimneys. No products move. Diff shown, nothing moved yet.</t>
+          <t>True duplicate, all 8 products in both. Merge attempted 7 Sept and REVERTED: urlRedirectCreate requires write_online_store_navigation, which is not granted, so unpublishing left /collections/chimney-option returning 404 with no redirect. Restored to Online Store. Needs the scope, or a manual redirect in the admin first.</t>
         </is>
       </c>
     </row>
@@ -5941,6 +6065,60 @@
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Position-tested and found not to be a round: 866 addressable page-one impressions once the dropped german article is excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>BBQ island filed under fireplaces</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>/collections/outdoor-fireplaces</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>YOU DECIDE</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>SKU: Cal Flame FRP906-2 BBQ Island - Full-Size Outdoor Kitchen ($ Cal Flame). It is an outdoor kitchen island sitting in a fireplace collection. Wrong for a buyer regardless of SEO scope - outdoor cooking being out of scope for COPY does not mean products should sit in the wrong collection. Move to /collections/outdoor-kitchen, which holds 14 comparable islands. Found by reading titles; productType could not surface it, as it is typed "Fire Pits" like its neighbours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Two collections wrongly scoped out</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>/collections/kohler, /collections/delta</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>REVERSED</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Both were in the client list of 11 outdoor-cooking collections. Neither is outdoor cooking. kohler holds 2 Kohler INDOOR SAUNAS ($17,867 and $18,667, also in /indoor-sauna). delta holds 7 Delta STEAM GENERATORS ($2,470-$12,009, also in /steam-showers). Both returned to the sweep; worksheet 66 -&gt; 68 rows. Found by auditing the 11 by product title rather than by collection name.</t>
         </is>
       </c>
     </row>
